--- a/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
+++ b/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\006-Diago\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A035A4C-3BC3-4CFD-851D-F3B0F55D862B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3948D036-31B2-42B2-8BE2-4DB4920969E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -1067,7 +1067,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1077,12 +1077,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1738,7 +1732,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2151,18 +2145,6 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2288,6 +2270,15 @@
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2594,61 +2585,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="169" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="175"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="171"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="176" t="s">
+      <c r="A2" s="172" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
-      <c r="H2" s="178"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="179"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="180"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="176"/>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="181" t="s">
+      <c r="A4" s="177" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="182"/>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="183"/>
+      <c r="B4" s="178"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="179"/>
     </row>
     <row r="5" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="83" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="184" t="s">
+      <c r="B5" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="185"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="94" t="s">
         <v>231</v>
       </c>
@@ -2656,10 +2647,10 @@
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="184" t="s">
+      <c r="F5" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="185"/>
+      <c r="G5" s="181"/>
       <c r="H5" s="83" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -2817,10 +2808,10 @@
       <c r="E14" s="85">
         <v>1228170</v>
       </c>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="206" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="165">
+      <c r="G14" s="207">
         <f>'FD Sch_2'!D81</f>
         <v>1523053</v>
       </c>
@@ -2836,16 +2827,16 @@
       <c r="E15" s="85">
         <v>67712</v>
       </c>
-      <c r="F15" s="166" t="s">
+      <c r="F15" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="167">
-        <f>'FD Sch_2'!G81+4</f>
-        <v>76530</v>
+      <c r="G15" s="118">
+        <f>'FD Sch_2'!G81</f>
+        <v>76526</v>
       </c>
       <c r="H15" s="35">
         <f>SUM(G13:G15)</f>
-        <v>1600583</v>
+        <v>1600579</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -3188,11 +3179,11 @@
       </c>
       <c r="C34" s="163">
         <f>-IE!H50</f>
-        <v>-670</v>
+        <v>-674</v>
       </c>
       <c r="D34" s="95">
         <f>SUM(C31:C34)</f>
-        <v>270259.45999999973</v>
+        <v>270255.45999999973</v>
       </c>
       <c r="E34" s="85"/>
       <c r="F34" s="41"/>
@@ -3204,25 +3195,25 @@
         <f>SUM(A10:A34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="172"/>
+      <c r="C35" s="168"/>
       <c r="D35" s="92">
         <f>SUM(D10:D34)</f>
-        <v>4162014.46</v>
+        <v>4162010.46</v>
       </c>
       <c r="E35" s="86">
         <f>SUM(E6:E34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="F35" s="172" t="s">
+      <c r="F35" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="172"/>
+      <c r="G35" s="168"/>
       <c r="H35" s="82">
         <f>SUM(H6:H34)</f>
-        <v>4162014.46</v>
+        <v>4162010.46</v>
       </c>
     </row>
     <row r="36" spans="1:13" customFormat="1" ht="7.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -3247,12 +3238,12 @@
       <c r="B37" s="66"/>
       <c r="C37" s="67"/>
       <c r="D37" s="66"/>
-      <c r="E37" s="170" t="s">
+      <c r="E37" s="166" t="s">
         <v>297</v>
       </c>
-      <c r="F37" s="170"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="171"/>
+      <c r="F37" s="166"/>
+      <c r="G37" s="166"/>
+      <c r="H37" s="167"/>
       <c r="I37" s="67"/>
       <c r="J37" s="66"/>
       <c r="K37" s="66"/>
@@ -3298,12 +3289,12 @@
       </c>
       <c r="B42" s="75"/>
       <c r="C42" s="76"/>
-      <c r="E42" s="170" t="s">
+      <c r="E42" s="166" t="s">
         <v>294</v>
       </c>
-      <c r="F42" s="170"/>
-      <c r="G42" s="170"/>
-      <c r="H42" s="171"/>
+      <c r="F42" s="166"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
       <c r="I42" s="67"/>
     </row>
     <row r="43" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3319,11 +3310,11 @@
       <c r="I43" s="67"/>
     </row>
     <row r="44" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="168">
+      <c r="A44" s="164">
         <v>46221</v>
       </c>
-      <c r="B44" s="169"/>
-      <c r="C44" s="169"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="165"/>
       <c r="H44" s="71"/>
       <c r="I44" s="67"/>
     </row>
@@ -3377,64 +3368,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="188" t="str">
+      <c r="A1" s="184" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="190"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="186"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="191" t="str">
+      <c r="A2" s="187" t="str">
         <f>BS!A2</f>
         <v>186-A, Baudi Cross Lane, Orlem, Malad (West), Mumbai, Maharashtra - 400064</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
-      <c r="H2" s="192"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="188"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="191" t="str">
+      <c r="A3" s="187" t="str">
         <f>BS!A3</f>
         <v>Society Reg No : BOM/(WP)/HSG(TC) 1007/84-85 dated.13/07/1984</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="192"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="188"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="189" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="182"/>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="194"/>
+      <c r="B4" s="178"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="190"/>
     </row>
     <row r="5" spans="1:10" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="97" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="195" t="s">
+      <c r="B5" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="195"/>
+      <c r="C5" s="191"/>
       <c r="D5" s="87" t="s">
         <v>231</v>
       </c>
@@ -3442,10 +3433,10 @@
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="195" t="s">
+      <c r="F5" s="191" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="195"/>
+      <c r="G5" s="191"/>
       <c r="H5" s="98" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -3911,7 +3902,8 @@
         <v>50</v>
       </c>
       <c r="C29" s="47">
-        <v>3420</v>
+        <f>3420+4</f>
+        <v>3424</v>
       </c>
       <c r="D29" s="88"/>
       <c r="E29" s="41"/>
@@ -4043,7 +4035,7 @@
       </c>
       <c r="D37" s="88">
         <f>SUM(C28:C37)</f>
-        <v>38506</v>
+        <v>38510</v>
       </c>
       <c r="E37" s="85"/>
       <c r="F37" s="36"/>
@@ -4240,7 +4232,7 @@
       <c r="G50" s="36"/>
       <c r="H50" s="37">
         <f>D52-SUM(H7:H47)</f>
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4265,25 +4257,25 @@
         <f>SUM(A6:A51)</f>
         <v>517077</v>
       </c>
-      <c r="B52" s="172" t="s">
+      <c r="B52" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="172"/>
+      <c r="C52" s="168"/>
       <c r="D52" s="92">
         <f>SUM(D6:D51)</f>
-        <v>531559</v>
+        <v>531563</v>
       </c>
       <c r="E52" s="86">
         <f>SUM(E6:E51)</f>
         <v>517077</v>
       </c>
-      <c r="F52" s="172" t="s">
+      <c r="F52" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="172"/>
+      <c r="G52" s="168"/>
       <c r="H52" s="100">
         <f>SUM(H6:H51)</f>
-        <v>531559</v>
+        <v>531563</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4309,12 +4301,12 @@
       <c r="B54" s="66"/>
       <c r="C54" s="67"/>
       <c r="D54" s="66"/>
-      <c r="E54" s="170" t="s">
+      <c r="E54" s="166" t="s">
         <v>297</v>
       </c>
-      <c r="F54" s="170"/>
-      <c r="G54" s="170"/>
-      <c r="H54" s="187"/>
+      <c r="F54" s="166"/>
+      <c r="G54" s="166"/>
+      <c r="H54" s="183"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="104"/>
@@ -4370,12 +4362,12 @@
       </c>
       <c r="B59" s="75"/>
       <c r="C59" s="76"/>
-      <c r="E59" s="170" t="s">
+      <c r="E59" s="166" t="s">
         <v>294</v>
       </c>
-      <c r="F59" s="170"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="187"/>
+      <c r="F59" s="166"/>
+      <c r="G59" s="166"/>
+      <c r="H59" s="183"/>
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4391,11 +4383,11 @@
       <c r="I60" s="67"/>
     </row>
     <row r="61" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="186">
+      <c r="A61" s="182">
         <v>46221</v>
       </c>
-      <c r="B61" s="169"/>
-      <c r="C61" s="169"/>
+      <c r="B61" s="165"/>
+      <c r="C61" s="165"/>
       <c r="H61" s="105"/>
       <c r="I61" s="67"/>
     </row>
@@ -4492,20 +4484,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="169" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="175"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="171"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="192" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="198"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="194"/>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
@@ -5121,37 +5113,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="199" t="str">
+      <c r="A1" s="195" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="197" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="201"/>
-      <c r="K2" s="201"/>
-      <c r="L2" s="201"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
     </row>
     <row r="3" spans="1:14" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
@@ -6992,37 +6984,37 @@
       <c r="O53" s="30"/>
     </row>
     <row r="54" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="199" t="str">
+      <c r="A54" s="195" t="str">
         <f>+A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B54" s="200"/>
-      <c r="C54" s="200"/>
-      <c r="D54" s="200"/>
-      <c r="E54" s="200"/>
-      <c r="F54" s="200"/>
-      <c r="G54" s="200"/>
-      <c r="H54" s="200"/>
-      <c r="I54" s="200"/>
-      <c r="J54" s="200"/>
-      <c r="K54" s="200"/>
-      <c r="L54" s="200"/>
+      <c r="B54" s="196"/>
+      <c r="C54" s="196"/>
+      <c r="D54" s="196"/>
+      <c r="E54" s="196"/>
+      <c r="F54" s="196"/>
+      <c r="G54" s="196"/>
+      <c r="H54" s="196"/>
+      <c r="I54" s="196"/>
+      <c r="J54" s="196"/>
+      <c r="K54" s="196"/>
+      <c r="L54" s="196"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="201" t="s">
+      <c r="A55" s="197" t="s">
         <v>269</v>
       </c>
-      <c r="B55" s="201"/>
-      <c r="C55" s="201"/>
-      <c r="D55" s="201"/>
-      <c r="E55" s="201"/>
-      <c r="F55" s="201"/>
-      <c r="G55" s="201"/>
-      <c r="H55" s="201"/>
-      <c r="I55" s="201"/>
-      <c r="J55" s="201"/>
-      <c r="K55" s="201"/>
-      <c r="L55" s="201"/>
+      <c r="B55" s="197"/>
+      <c r="C55" s="197"/>
+      <c r="D55" s="197"/>
+      <c r="E55" s="197"/>
+      <c r="F55" s="197"/>
+      <c r="G55" s="197"/>
+      <c r="H55" s="197"/>
+      <c r="I55" s="197"/>
+      <c r="J55" s="197"/>
+      <c r="K55" s="197"/>
+      <c r="L55" s="197"/>
     </row>
     <row r="56" spans="1:15" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
@@ -7922,29 +7914,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="202" t="str">
+      <c r="A1" s="198" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="204" t="s">
+      <c r="A2" s="200" t="s">
         <v>249</v>
       </c>
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
     </row>
     <row r="3" spans="1:8" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="140" t="s">
@@ -8218,34 +8210,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="str">
+      <c r="A1" s="205" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="173" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="G2" s="177" t="s">
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="G2" s="173" t="s">
         <v>245</v>
       </c>
-      <c r="H2" s="177"/>
-      <c r="I2" s="177"/>
-      <c r="J2" s="177"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="154" t="s">
@@ -8307,12 +8299,12 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="206" t="s">
+      <c r="A5" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="207"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="162">
         <f>SUM(E4:E4)</f>
         <v>3982</v>
@@ -8345,13 +8337,13 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="201" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
       <c r="G7" s="143">
         <v>4</v>
       </c>
@@ -8382,11 +8374,11 @@
       <c r="E8" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="206" t="s">
+      <c r="G8" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="207"/>
-      <c r="I8" s="208"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="204"/>
       <c r="J8" s="161">
         <f>SUM(J4:J7)</f>
         <v>33044</v>
@@ -8450,12 +8442,12 @@
       <c r="L11" s="150"/>
     </row>
     <row r="12" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="206" t="s">
+      <c r="A12" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="207"/>
-      <c r="C12" s="207"/>
-      <c r="D12" s="208"/>
+      <c r="B12" s="203"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="204"/>
       <c r="E12" s="161">
         <f>SUM(E9:E11)</f>
         <v>21383</v>
@@ -8468,13 +8460,13 @@
       <c r="L13" s="150"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="205" t="s">
+      <c r="A14" s="201" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="201"/>
       <c r="G14" s="135"/>
       <c r="L14" s="150"/>
     </row>
